--- a/assingment/excel assingment/session -11/SESSION-11.xlsx
+++ b/assingment/excel assingment/session -11/SESSION-11.xlsx
@@ -1,26 +1,136 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\Tops\assingment\excel assingment\session -11\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BB6C0C-AF71-4AF1-830D-5706DA61600A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="TASK -1" sheetId="1" r:id="rId1"/>
+    <sheet name="TASK-2" sheetId="2" r:id="rId2"/>
+    <sheet name="TASK - 3" sheetId="3" r:id="rId3"/>
+    <sheet name="TASK -4" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>CSK</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>Gujarat Titans</t>
+  </si>
+  <si>
+    <t>RCB</t>
+  </si>
+  <si>
+    <t>RESULT</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Ahmedabad</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>iPhone 15</t>
+  </si>
+  <si>
+    <t>Galaxy S24</t>
+  </si>
+  <si>
+    <t>OnePlus 12</t>
+  </si>
+  <si>
+    <t>Song</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>Kesariya</t>
+  </si>
+  <si>
+    <t>Apna Bana Le</t>
+  </si>
+  <si>
+    <t>Chaleya</t>
+  </si>
+  <si>
+    <t>Restaurant</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>Pizza Point</t>
+  </si>
+  <si>
+    <t>Burger Hub</t>
+  </si>
+  <si>
+    <t>Food Plaza</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,13 +138,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,8 +173,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +464,325 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>45383</v>
+      </c>
+      <c r="C1" s="2">
+        <v>45390</v>
+      </c>
+      <c r="D1" s="2">
+        <v>45397</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3">
+        <v>180</v>
+      </c>
+      <c r="C2" s="3">
+        <v>175</v>
+      </c>
+      <c r="D2" s="3">
+        <v>190</v>
+      </c>
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3">
+        <v>165</v>
+      </c>
+      <c r="C3" s="3">
+        <v>182</v>
+      </c>
+      <c r="D3" s="3">
+        <v>178</v>
+      </c>
+      <c r="F3">
+        <f>INDEX($A$1:$D$5,MATCH($A$4,$A$1:$A$5,0),MATCH($D$1,$A$1:$D$1))</f>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>170</v>
+      </c>
+      <c r="C4" s="3">
+        <v>188</v>
+      </c>
+      <c r="D4" s="3">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>160</v>
+      </c>
+      <c r="C5" s="3">
+        <v>172</v>
+      </c>
+      <c r="D5" s="3">
+        <v>185</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB694473-A44D-42E6-A9A6-71316BAC9AC3}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="3">
+        <v>72000</v>
+      </c>
+      <c r="C2" s="3">
+        <v>71500</v>
+      </c>
+      <c r="D2" s="3">
+        <v>71800</v>
+      </c>
+      <c r="F2">
+        <f>INDEX($A$1:$D$4,MATCH($A$3,$A$1:$A$4,0),MATCH($B$1,$A$1:$D$1,0))</f>
+        <v>68000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3">
+        <v>68000</v>
+      </c>
+      <c r="C3" s="3">
+        <v>67500</v>
+      </c>
+      <c r="D3" s="3">
+        <v>67800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3">
+        <v>60000</v>
+      </c>
+      <c r="C4" s="3">
+        <v>59800</v>
+      </c>
+      <c r="D4" s="3">
+        <v>60200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ABB62D4-776A-46A7-8A9D-75B669269D55}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="3">
+        <v>150</v>
+      </c>
+      <c r="C2" s="3">
+        <v>170</v>
+      </c>
+      <c r="D2" s="3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="3">
+        <v>120</v>
+      </c>
+      <c r="C3" s="3">
+        <v>145</v>
+      </c>
+      <c r="D3" s="3">
+        <v>160</v>
+      </c>
+      <c r="F3" s="4">
+        <f>INDEX($A$1:$D$4,MATCH(A$2,$A$1:$A$4,0),MATCH($D$1,$A$1:$D$1,0))</f>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="3">
+        <v>140</v>
+      </c>
+      <c r="C4" s="3">
+        <v>155</v>
+      </c>
+      <c r="D4" s="3">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{682FFB3E-18B9-4322-9051-7DAA7C7243C1}">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C2" s="3">
+        <v>2800</v>
+      </c>
+      <c r="D2" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E2" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F2" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I2">
+        <f>INDEX($A$1:$F$4,MATCH($A$3,$A$1:$A$4,0),MATCH($F$1,$A$1:$F$1,0))</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1800</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1900</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E3" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="3">
+        <v>3200</v>
+      </c>
+      <c r="C4" s="3">
+        <v>3300</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F4" s="3">
+        <v>3900</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>